--- a/upload/report/test_hiraoka21.xlsx
+++ b/upload/report/test_hiraoka21.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="98">
   <si>
     <t>Purchase order items PDF to Excel</t>
   </si>
@@ -23,7 +23,16 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02 19:27:54</t>
+    <t>2024-04-03 11:34:49</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>#Order</t>
   </si>
   <si>
     <t>Num</t>
@@ -44,7 +53,16 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Product</t>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>IMPORTACIONES HIRAOKA S.A.C.</t>
+  </si>
+  <si>
+    <t>CALLE 5, MZ. D-1, LOTE 5 - COOP., LAS VER VILLA EL SALVADOR</t>
+  </si>
+  <si>
+    <t>132673</t>
   </si>
   <si>
     <t>1</t>
@@ -59,7 +77,13 @@
     <t>130</t>
   </si>
   <si>
-    <t xml:space="preserve"> 800.9700 104,126.10MINICOMPONENTE LG - CJ45</t>
+    <t>800.9700</t>
+  </si>
+  <si>
+    <t>104,126.10</t>
+  </si>
+  <si>
+    <t>MINICOMPONENTE LG - CJ45</t>
   </si>
   <si>
     <t>2</t>
@@ -71,7 +95,13 @@
     <t>80</t>
   </si>
   <si>
-    <t xml:space="preserve"> 659.4700 52,757.60MINICOMPONENTE LG - RNC5</t>
+    <t>659.4700</t>
+  </si>
+  <si>
+    <t>52,757.60</t>
+  </si>
+  <si>
+    <t>MINICOMPONENTE LG - RNC5</t>
   </si>
   <si>
     <t>3</t>
@@ -83,7 +113,13 @@
     <t>95</t>
   </si>
   <si>
-    <t xml:space="preserve"> 798.4600 75,853.70MINICOMPONENTE LG - RNC7</t>
+    <t>798.4600</t>
+  </si>
+  <si>
+    <t>75,853.70</t>
+  </si>
+  <si>
+    <t>MINICOMPONENTE LG - RNC7</t>
   </si>
   <si>
     <t>4</t>
@@ -113,7 +149,13 @@
     <t>12</t>
   </si>
   <si>
-    <t xml:space="preserve"> 325.6800  3,908.16PARLANTE LG - PL7</t>
+    <t>325.6800</t>
+  </si>
+  <si>
+    <t>3,908.16</t>
+  </si>
+  <si>
+    <t>PARLANTE LG - PL7</t>
   </si>
   <si>
     <t>6</t>
@@ -125,7 +167,13 @@
     <t>15</t>
   </si>
   <si>
-    <t xml:space="preserve"> 414.6600  6,219.90PARLANTE LG - XG7QBK</t>
+    <t>414.6600</t>
+  </si>
+  <si>
+    <t>6,219.90</t>
+  </si>
+  <si>
+    <t>PARLANTE LG - XG7QBK</t>
   </si>
   <si>
     <t>7</t>
@@ -179,7 +227,13 @@
     <t>130434</t>
   </si>
   <si>
-    <t xml:space="preserve"> 446.7100  4,467.10SOUNDBAR LG - SQC1</t>
+    <t>446.7100</t>
+  </si>
+  <si>
+    <t>4,467.10</t>
+  </si>
+  <si>
+    <t>SOUNDBAR LG - SQC1</t>
   </si>
   <si>
     <t>11</t>
@@ -191,7 +245,13 @@
     <t>20</t>
   </si>
   <si>
-    <t xml:space="preserve"> 436.5600  8,731.20MINICOMPONENTE LG - CK43N</t>
+    <t>436.5600</t>
+  </si>
+  <si>
+    <t>8,731.20</t>
+  </si>
+  <si>
+    <t>MINICOMPONENTE LG - CK43N</t>
   </si>
   <si>
     <t>131770</t>
@@ -200,7 +260,13 @@
     <t>100</t>
   </si>
   <si>
-    <t xml:space="preserve"> 829.9200 82,992.00PARLANTE LG - XG8T</t>
+    <t>829.9200</t>
+  </si>
+  <si>
+    <t>82,992.00</t>
+  </si>
+  <si>
+    <t>PARLANTE LG - XG8T</t>
   </si>
   <si>
     <t>13</t>
@@ -582,15 +648,15 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -598,7 +664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -620,318 +686,494 @@
       <c r="G4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5"/>
-      <c r="F5"/>
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
       <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6"/>
-      <c r="F6"/>
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
       <c r="G6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7"/>
-      <c r="F7"/>
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
       <c r="G7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>37</v>
+      </c>
+      <c r="H8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9"/>
-      <c r="F9"/>
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
       <c r="G9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" t="s">
+        <v>66</v>
+      </c>
+      <c r="I13" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
         <v>35</v>
       </c>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="H17" t="s">
+        <v>86</v>
+      </c>
+      <c r="I17" t="s">
+        <v>87</v>
+      </c>
+      <c r="J17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" t="s">
+        <v>92</v>
+      </c>
+      <c r="J18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
         <v>49</v>
       </c>
-      <c r="E13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
-        <v>60</v>
-      </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="G19" t="s">
-        <v>75</v>
+        <v>80</v>
+      </c>
+      <c r="H19" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
